--- a/data_extactor/batch_10_fa/batch_0072_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0072_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Bentley STAAD | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | نرم‌افزار برآورد هزینه | Esri ArcGIS | نرم‌افزار ردیابی موجودی | نرم‌افزار نقشه‌برداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint Server | Microsoft Visio | Microsoft Windows | Microsoft Word | Minitab | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera Systems | PVsyst | نرم‌افزار Procore | Prolog | نرم‌افزار سیستم‌عامل بی‌درنگ RTOS | نرم‌افزار SAP | نرم‌افزار Salesforce | Trimble SketchUp Pro | نرم‌افزار زمان‌بندی کار</t>
+          <t>Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Bentley STAAD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار برآورد هزینه | Esri ArcGIS | نرم‌افزار ردیابی موجودی | نرم‌افزار نقشه‌برداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint Server | Microsoft Visio | Microsoft Windows | Microsoft Word | Minitab | Oracle Primavera Enterprise Project Portfolio Management | Oracle Primavera Systems | PVsyst | Procore software | Prolog | نرم‌افزار سیستم‌عامل بلادرنگ RTOS | نرم‌افزار SAP | نرم‌افزار Salesforce | Trimble SketchUp Pro | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>پایش | درک مطلب | سخن‌گفتن | گوش‌دادن فعالانه | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
+          <t>نظارت | درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | خدمات مشتریان و شخصی | امور اداری و مدیریت | طراحی | مکانیک | حمل‌ونقل | فروش و بازاریابی | ریاضیات</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مدیریت و اداره | طراحی | مکانیک | حمل و نقل | فروش و بازاریابی | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | سازماندهی اطلاعات | استدلال استقرایی | بیان کتبی | تجسم فضایی | بینایی دور | وضوح گفتار | تشخیص گفتار | ثبات دست و بازو | دقت کنترل | زبردستی دستی | تشخیص رنگ بصری | توجه انتخابی | انعطاف‌پذیری ساختار | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی | تجسم | بینایی دور | وضوح گفتار | تشخیص گفتار | ثبات دست و بازو | دقت کنترل | مهارت دستی | تشخیص رنگ بصری | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>تماس با دیگران | ایمیل | مکالمات تلفنی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا منظم بودن | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | سلامت و ایمنی سایر کارکنان | در معرض دمای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه یا تیم کاری | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | صرف زمان به حالت ایستاده | در معرض ارتفاعات بالا | در معرض شرایط خطرناک | سطح رقابت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض آلاینده‌ها | اهمیت تکرار وظایف مشابه | پیامد خطا</t>
+          <t>ارتباط با دیگران | ایمیل | مکالمات تلفنی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | قرار گرفتن در معرض ارتفاعات بالا | قرار گرفتن در معرض شرایط خطرناک | سطح رقابت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | پیامد خطا</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>معماران، به جز منظر و دریایی | مهندسان عمران | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | مهندسان برق | برق‌کاران | ممیزان انرژی | مهندسان انرژی، به جز باد و خورشید | سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | مدیران تولید زمین‌گرمایی | مهندسان صنایع | کارگران نگهداری و تعمیرات، عمومی | متخصصان مدیریت پروژه | مهندسان سیستم‌های انرژی خورشیدی | نصب‌کنندگان فتوولتائیک خورشیدی | نمایندگان فروش و ارزیابان خورشیدی | نصب‌کنندگان و تکنسین‌های حرارتی خورشیدی | نصب‌کنندگان و تکنسین‌های عایق‌سازی هوا | مدیران توسعه انرژی بادی</t>
+          <t>معماران، به‌جز منظر و دریایی | مهندسان عمران | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | مهندسان برق | برق‌کاران | بازرسان انرژی | مهندسان انرژی، به جز باد و خورشید | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | مدیران تولید زمین‌گرمایی | مهندسان صنایع | کارگران نگهداری و تعمیرات عمومی | متخصصان مدیریت پروژه | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | نمایندگان و ارزیابان فروش تجهیزات خورشیدی | نصابان و تکنسین‌های حرارتی خورشیدی | نصابان و تکنسین‌های عایق‌سازی و مقاوم‌سازی در برابر شرایط جوی | مدیران توسعه انرژی بادی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Boilermakers</t>
+          <t>دیگ‌سازان (Boilermakers)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | پایش | یادگیری فعال | سخن‌گفتن | گوش‌دادن فعالانه | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | ثبات دست و بازو | زبردستی دستی | زبردستی انگشتان | هماهنگی چند عضو | استدلال استقرایی | درک شفاهی | وضوح گفتار | توجه شنیداری | بینایی دور | انعطاف‌پذیری بدنی | قدرت بالاتنه | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری ساختار | انعطاف‌پذیری دسته‌بندی | سازماندهی اطلاعات | روان بودن ایده‌ها | بیان کتبی | بیان شفاهی | درک کتبی</t>
+          <t>دقت کنترل | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | هماهنگی چند عضو | استدلال استقرایی | درک شفاهی | وضوح گفتار | توجه شنیداری | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | بیان کتبی | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | تماس با دیگران | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا منظم بودن | کار با یا مشارکت در یک گروه یا تیم کاری | داخل ساختمان، با دمای کنترل‌شده | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | در معرض دمای بسیار گرم یا سرد | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | صرف زمان به حالت ایستاده | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان، بدون دمای کنترل‌شده | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | پیامدهای کاری و نتایج سایر کارکنان | در معرض سوختگی‌های جزئی، بریدگی‌ها، گزیدگی‌ها یا نیش‌زدگی‌ها | نزدیکی فیزیکی</t>
+          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، بدون کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | نصب‌کنندگان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌ها و نصب‌کنندگان گرمایش، تهویه مطبوع و تبرید | کمک‌برق‌کاران | کمک‌نصب‌کنندگان، کارگران نگهداری و تعمیرات | کمک‌لوله‌کشان، لوله‌کشان صنعتی و بخار | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات، عمومی | سازندگان آسیاب و ماشین‌آلات صنعتی | لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران ورق‌کاری | مهندسان تاسیسات و اپراتورهای دیگ بخار | کارگران اسکلت فلزی و فولادی | سازندگان و جفت‌کنندگان فلزات سازه‌ای | جوشکاران، برش‌کاران، لحیم‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری و لحیم‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--برق‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران ورق‌کاری | مهندسان تاسیسات و اپراتورهای دیگ بخار | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brickmasons and Blockmasons</t>
+          <t>بنّایان آجرکار و بلوک‌کار (Brickmasons and Blockmasons)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CPR Visual Estimator | نرم‌افزار مدیریت ساخت ProEst | Daystar iStructural.com | نرم‌افزار برآورد | Intuit QuickBooks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | RISA Technologies RISA-3D | Tradesman's Software Master Estimator</t>
+          <t>CPR Visual Estimator | نرم‌افزار مدیریت ساخت ProEst | Daystar iStructural.com | Estimating software | Intuit QuickBooks | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | RISA Technologies RISA-3D | Tradesman's Software Master Estimator</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | پایش | سخن‌گفتن | گوش‌دادن فعالانه</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | تولید و فرآوری | طراحی | امور اداری و مدیریت | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | تولید و فرآوری | طراحی | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>قدرت بالاتنه | انعطاف‌پذیری بدنی | بینایی نزدیک | ثبات دست و بازو | زبردستی دستی | قدرت ایستا | تجسم فضایی | هماهنگی چند عضو | قدرت پویا | سازماندهی اطلاعات | زبردستی انگشتان | حساسیت به مسئله | تعادل عمومی بدن | بینایی دور | هماهنگی عمومی بدن | استقامت بدنی | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی | درک کتبی</t>
+          <t>قدرت تنه | انعطاف‌پذیری دامنه حرکت | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | قدرت ایستا | تجسم | هماهنگی چند عضو | قدرت پویا | ترتیب‌دهی اطلاعات | مهارت انگشتان | حساسیت به مسئله | تعادل کلی بدن | بینایی دور | هماهنگی کلی بدن | استقامت | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک, دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان به حالت ایستاده | در معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در معرض دمای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | در معرض ارتفاعات بالا | کار با یا مشارکت در یک گروه یا تیم کاری | در معرض آلاینده‌ها | صرف زمان برای بالا رفتن از نردبان، داربست یا تیرها | مکالمات تلفنی | اهمیت دقیق یا منظم بودن | صرف زمان برای خم شدن یا چرخاندن بدن | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | داخل ساختمان، بدون دمای کنترل‌شده | تماس با دیگران | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | در معرض سوختگی‌های جزئی، بریدگی‌ها، گزیدگی‌ها یا نیش‌زدگی‌ها | در معرض شرایط نوری بسیار روشن یا ناکافی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | قرار گرفتن در معرض ارتفاعات بالا | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>دیگ‌سازان | نجاران | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصب‌کنندگان دیوار خشک و تایل سقف | کف‌سازان، به جز فرش، چوب و تایل‌های سخت | شیشه‌بران | کمک‌بناهای آجرچین، بلوک‌چین، سنگ‌چین و نصب‌کنندگان تایل و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | گچ‌کاران و بناهای سیمان‌کار | تعمیرکاران مواد نسوز، به جز بناهای آجرچین | کارگران آرماتوربند و میلگرد | کارگران ورق‌کاری | سنگ‌چین‌ها | کارگران اسکلت فلزی و فولادی | سازندگان و جفت‌کنندگان فلزات سازه‌ای | کارگران موزاییک‌ساز و پرداخت‌کار | نصب‌کنندگان تایل و سنگ</t>
+          <t>دیگ‌سازان | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | شیشه‌بران | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | گچ‌کاران و بناهای سیمان‌کاری | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | کارگران آهن تقویتی و میلگرد | کارگران ورق‌کاری | بنّایان سنگ‌کار | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stonemasons</t>
+          <t>بنّایان سنگ‌کار (Stonemasons)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CPR Visual Estimator | نرم‌افزار محاسبات ابری Citrix | Gregg Software Gregg Rock-It | Intuit QuickBooks | صفحات سرور فعال مایکروسافت ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | ProEst Software ProEst Estimating | RISA Technologies RISA-3D | نرم‌افزار SAP | Tradesman&amp;apos;s Software Master Estimator | نرم‌افزار شبکه خصوصی مجازی VPN</t>
+          <t>CPR Visual Estimator | نرم‌افزار رایانش ابری Citrix | Gregg Software Gregg Rock-It | Intuit QuickBooks | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | ProEst Software ProEst Estimating | RISA Technologies RISA-3D | نرم‌افزار SAP | Tradesman&amp;apos;s Software Master Estimator | نرم‌افزار شبکه خصوصی مجازی VPN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش‌دادن فعالانه | درک مطلب | پایش | ریاضیات | سخن‌گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نظارت | ریاضیات | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | طراحی | ریاضیات | مکانیک | خدمات مشتریان و شخصی | امور اداری و مدیریت | زبان انگلیسی</t>
+          <t>ساختمان و ساخت‌وساز | طراحی | ریاضیات | مکانیک | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>قدرت ایستا | قدرت بالاتنه | بینایی نزدیک | ثبات دست و بازو | زبردستی دستی | حساسیت به مسئله | تجسم فضایی | استقامت بدنی | بینایی دور | انعطاف‌پذیری بدنی | هماهنگی چند عضو | سازماندهی اطلاعات | درک شفاهی | توجه انتخابی | زبردستی انگشتان | قدرت پویا | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | تعادل عمومی بدن | دقت کنترل | بیان شفاهی | وضوح گفتار | تشخیص گفتار</t>
+          <t>قدرت ایستا | قدرت تنه | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | حساسیت به مسئله | تجسم | استقامت | بینایی دور | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | ترتیب‌دهی اطلاعات | درک شفاهی | توجه انتخابی | مهارت انگشتان | قدرت پویا | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | تعادل کلی بدن | دقت کنترل | بیان شفاهی | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه یا تیم کاری | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به حالت ایستاده | اهمیت دقیق یا منظم بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | در معرض آلاینده‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | مکالمات تلفنی | در معرض تجهیزات خطرناک | صرف زمان برای خم شدن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارکنان | تماس با دیگران | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | در معرض دمای بسیار گرم یا سرد | پیامد خطا | فشار زمانی</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | مکالمات تلفنی | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای خم کردن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارکنان | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامد خطا | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بناهای آجرچین و بلوک‌چین | نجاران | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصب‌کنندگان دیوار خشک و تایل سقف | کف‌سازان، به جز فرش، چوب و تایل‌های سخت | سنباده‌کشان و پرداخت‌کاران کف | شیشه‌بران | کمک‌بناهای آجرچین، بلوک‌چین، سنگ‌چین و نصب‌کنندگان تایل و مرمر | کمک‌نجاران | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | گچ‌کاران و بناهای سیمان‌کار | تعمیرکاران مواد نسوز، به جز بناهای آجرچین | کارگران آرماتوربند و میلگرد | سقف‌سازان | سنگ‌فرش‌کنان قطعه‌ای | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | کارگران اسکلت فلزی و فولادی | کارگران موزاییک‌ساز و پرداخت‌کار | نصب‌کنندگان تایل و سنگ</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | سنباده‌کاران و پرداخت‌کاران کف | شیشه‌بران | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | گچ‌کاران و بناهای سیمان‌کاری | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | کارگران آهن تقویتی و میلگرد | سقف‌سازان | سنگ‌فرش‌کاران قطعه‌ای | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | کارگران سازه‌های آهنی و فولادی | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carpenters</t>
+          <t>نجّاران (Carpenters)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bosch Punch List | Craftsman CD Estimator | نرم‌افزار ترسیم و طراحی | نرم‌افزار برآورد | Intuit QuickBooks | نرم‌افزار بهای تمام شده پروژه | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | Quicken | Renaissance MasterCarpenter | Turtle Creek Software Goldenseal | VirtualBoss | نرم‌افزار مرورگر وب | Wilhelm Publishing Threshold</t>
+          <t>Bosch Punch List | Craftsman CD Estimator | نرم‌افزار ترسیم و طراحی | Estimating software | Intuit QuickBooks | نرم‌افزار هزینه‌یابی کار | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | Quicken | Renaissance MasterCarpenter | Turtle Creek Software Goldenseal | VirtualBoss | نرم‌افزار مرورگر وب | Wilhelm Publishing Threshold</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعالانه | تفکر انتقادی | پایش | درک مطلب | سخن‌گفتن | یادگیری فعال | ریاضیات</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | ریاضیات | امور اداری و مدیریت | طراحی | مهندسی و فناوری | ایمنی و امنیت عمومی | مکانیک | آموزش و تربیت | خدمات مشتریان و شخصی | فیزیک</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | مدیریت و اداره | طراحی | مهندسی و فناوری | ایمنی و امنیت عمومی | مکانیک | آموزش و پرورش | خدمات مشتری و شخصی | فیزیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | تجسم فضایی | بینایی نزدیک | زبردستی دستی | زبردستی انگشتان | قدرت بالاتنه | ثبات دست و بازو | سازماندهی اطلاعات | استدلال قیاسی | بینایی دور | هماهنگی چند عضو | بیان شفاهی | درک شفاهی | قدرت ایستا | استدلال استقرایی | زمان عکس‌العمل | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | قدرت انفجاری | سرعت ادراکی | انعطاف‌پذیری ساختار | درک کتبی</t>
+          <t>حساسیت به مسئله | تجسم | بینایی نزدیک | مهارت دستی | مهارت انگشتان | قدرت تنه | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | بینایی دور | هماهنگی چند عضو | بیان شفاهی | درک شفاهی | قدرت ایستا | استدلال استقرایی | زمان عکس‌العمل | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | قدرت انفجاری | سرعت ادراکی | انعطاف‌پذیری بستار | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | تماس با دیگران | صرف زمان به حالت ایستاده | اهمیت دقیق یا منظم بودن | کار با یا مشارکت در یک گروه یا تیم کاری | سلامت و ایمنی سایر کارکنان | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | فضای باز، در معرض تمام شرایط آب و هوایی | در معرض آلاینده‌ها | نزدیکی فیزیکی | پیامد خطا | در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای خم شدن یا چرخاندن بدن | در معرض ارتفاعات بالا</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض آلاینده‌ها | نزدیکی فیزیکی | پیامد خطا | قرار گرفتن در معرض تجهیزات خطرناک | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض ارتفاعات بالا</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | بناهای آجرچین و بلوک‌چین | کابینت‌سازان و نجاران کارگاهی | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصب‌کنندگان دیوار خشک و تایل سقف | کف‌سازان، به جز فرش، چوب و تایل‌های سخت | شیشه‌بران | کمک‌بناهای آجرچین، بلوک‌چین، سنگ‌چین و نصب‌کنندگان تایل و مرمر | کمک‌نجاران | کمک‌لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری کف، سقف و دیوار | کارگران پیاده‌سازی طرح، فلز و پلاستیک | گچ‌کاران و بناهای سیمان‌کار | کارگران آرماتوربند و میلگرد | سقف‌سازان | کارگران ورق‌کاری | کارگران اسکلت فلزی و فولادی | سازندگان و جفت‌کنندگان فلزات سازه‌ای | نصب‌کنندگان تایل و سنگ</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | بنّایان آجرکار و بلوک‌کار | کابینت‌سازان و نجاران نیمکت | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | شیشه‌بران | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری کف، سقف و دیوار | کارگران شابلون‌زنی، فلز و پلاستیک | گچ‌کاران و بناهای سیمان‌کاری | کارگران آهن تقویتی و میلگرد | سقف‌سازان | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carpet Installers</t>
+          <t>نصّابان موکت و فرش (Carpet Installers)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Aya Associates Comp-U-Floor | Carpet Dealer Management System CDMS | FIRST Flooring | FloorCOST Estimator for Excel | Flooring Technologies QFloors | Focus Floor Covering Software | Measure Square FloorEstimate Pro | Microsoft Excel | Microsoft Office software | Microsoft Word | Pacific Solutions FloorRight | RFMS Schedule Pro | Textile Management Systems RollMaster | eTakeoff</t>
+          <t>Autodesk AutoCAD | Aya Associates Comp-U-Floor | Carpet Dealer Management System CDMS | FIRST Flooring | FloorCOST Estimator for Excel | Flooring Technologies QFloors | Focus Floor Covering Software | Measure Square FloorEstimate Pro | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | Pacific Solutions FloorRight | RFMS Schedule Pro | Textile Management Systems RollMaster | eTakeoff</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | ریاضیات</t>
+          <t>نظارت | تفکر انتقادی | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ریاضیات | امور اداری و مدیریت | زبان انگلیسی | ساختمان و سازه | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره | زبان انگلیسی | ساختمان و ساخت‌وساز | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>انعطاف‌پذیری بدنی | قدرت بالاتنه | حساسیت به مسئله | بینایی نزدیک | قدرت ایستا | تشخیص گفتار | تجسم فضایی | ثبات دست و بازو | زبردستی دستی | بیان شفاهی | استقامت بدنی | هماهنگی چند عضو | زبردستی انگشتان | درک عمق | بینایی دور | قدرت پویا | توجه انتخابی | سازماندهی اطلاعات | استدلال قیاسی | درک شفاهی</t>
+          <t>انعطاف‌پذیری دامنه حرکت | قدرت تنه | حساسیت به مسئله | بینایی نزدیک | قدرت ایستا | تشخیص گفتار | تجسم | ثبات دست و بازو | مهارت دستی | بیان شفاهی | استقامت | هماهنگی چند عضو | مهارت انگشتان | درک عمق | بینایی دور | قدرت پویا | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | صرف زمان به حالت زانو زده، چمباتمه، خمیده یا خزیده | مکالمات تلفنی | تماس با دیگران | داخل ساختمان، با دمای کنترل‌شده | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | در معرض آلاینده‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا منظم بودن | کار با یا مشارکت در یک گروه یا تیم کاری | صرف زمان برای خم شدن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارکنان | در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در معرض سوختگی‌های جزئی، بریدگی‌ها، گزیدگی‌ها یا نیش‌زدگی‌ها</t>
+          <t>آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | مکالمات تلفنی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای خم کردن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بناهای آجرچین و بلوک‌چین | نجاران | سیمان‌کاران و پرداخت‌کاران بتن | نصب‌کنندگان دیوار خشک و تایل سقف | کف‌سازان، به جز فرش، چوب و تایل‌های سخت | سنباده‌کشان و پرداخت‌کاران کف | پرداخت‌کاران مبلمان | شیشه‌بران | کمک‌بناهای آجرچین، بلوک‌چین، سنگ‌چین و نصب‌کنندگان تایل و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کاغذدیواری‌کنان | گچ‌کاران و بناهای سیمان‌کار | سقف‌سازان | سنگ‌فرش‌کنان قطعه‌ای | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | کارگران موزاییک‌ساز و پرداخت‌کار | نصب‌کنندگان تایل و سنگ | رویه‌کوبان مبل</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | سنباده‌کاران و پرداخت‌کاران کف | پرداخت‌کاران مبلمان | شیشه‌بران | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کاغذدیواری‌کن‌ها | گچ‌کاران و بناهای سیمان‌کاری | سقف‌سازان | سنگ‌فرش‌کاران قطعه‌ای | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران | روکوبان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Floor Layers, Except Carpet, Wood, and Hard Tiles</t>
+          <t>کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت (Floor Layers, Except Carpet, Wood, and Hard Tiles)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aya Associates Comp-U-Floor | CPR Software FloorCOST Estimator for Excel | Facebook | Flooring Technologies QFloors | Focus Floor Covering Software | Measure Square FloorEstimate Pro | Microsoft Office software | On Center On-Screen Takeoff | Pacific Solutions FloorRight | نرم‌افزار تصویرسازی پروژه | نرم‌افزار شناسایی با فرکانس رادیویی RFID | Textile Management Systems RollMaster | نرم‌افزار مرورگر وب</t>
+          <t>Aya Associates Comp-U-Floor | CPR Software FloorCOST Estimator for Excel | Facebook | Flooring Technologies QFloors | Focus Floor Covering Software | Measure Square FloorEstimate Pro | نرم‌افزار Microsoft Office | On Center On-Screen Takeoff | Pacific Solutions FloorRight | نرم‌افزار تصویرسازی پروژه | نرم‌افزار شناسایی فرکانس رادیویی RFID | Textile Management Systems RollMaster | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعالانه | سخن‌گفتن</t>
+          <t>گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | خدمات مشتریان و شخصی | ریاضیات | مکانیک | تولید و فرآوری | طراحی</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | ریاضیات | مکانیک | تولید و فرآوری | طراحی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | انعطاف‌پذیری بدنی | ثبات دست و بازو | درک شفاهی | قدرت ایستا | زبردستی انگشتان | زبردستی دستی | حساسیت به مسئله | بیان شفاهی | وضوح گفتار | سازماندهی اطلاعات | استدلال قیاسی</t>
+          <t>بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | درک شفاهی | قدرت ایستا | مهارت انگشتان | مهارت دستی | حساسیت به مسئله | بیان شفاهی | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تماس با دیگران | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض آلاینده‌ها | صرف زمان برای به حالت زانو زده، چمباتمه، خمیده یا خزیده | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا منظم بودن | مکالمات تلفنی | صرف زمان برای خم شدن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | داخل ساختمان، با دمای کنترل‌شده | نزدیکی فیزیکی | در معرض تجهیزات خطرناک | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه یا تیم کاری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | مکالمات تلفنی | صرف زمان برای خم کردن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | محیط داخلی، دارای کنترل شرایط محیطی | نزدیکی فیزیکی | قرار گرفتن در معرض تجهیزات خطرناک | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بناهای آجرچین و بلوک‌چین | نجاران | فرش‌بندان | سیمان‌کاران و پرداخت‌کاران بتن | نصب‌کنندگان دیوار خشک و تایل سقف | سنباده‌کشان و پرداخت‌کاران کف | پرداخت‌کاران مبلمان | شیشه‌بران | کمک‌بناهای آجرچین، بلوک‌چین، سنگ‌چین و نصب‌کنندگان تایل و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کاغذدیواری‌کنان | گچ‌کاران و بناهای سیمان‌کار | سقف‌سازان | سنگ‌فرش‌کنان قطعه‌ای | کارگران ورق‌کاری | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | کارگران موزاییک‌ساز و پرداخت‌کار | نصب‌کنندگان تایل و سنگ</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | نصّابان موکت و فرش | بنّایان سیمان‌کار و پرداخت‌کاران بتن | نصابان دیوار خشک و تایل سقف | سنباده‌کاران و پرداخت‌کاران کف | پرداخت‌کاران مبلمان | شیشه‌بران | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کاغذدیواری‌کن‌ها | گچ‌کاران و بناهای سیمان‌کاری | سقف‌سازان | سنگ‌فرش‌کاران قطعه‌ای | کارگران ورق‌کاری | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Floor Sanders and Finishers</t>
+          <t>سنباده‌کاران و پرداخت‌کاران کف (Floor Sanders and Finishers)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار طراحی کف | FloorCOST Estimator for Excel | Flooring Technologies QFloors | Measure Square | Microsoft Excel | Pacific Solutions FloorRight | Vimeo</t>
+          <t>نرم‌افزار برنامه‌ریزی چیدمان طبقات | FloorCOST Estimator for Excel | Flooring Technologies QFloors | Measure Square | Microsoft Excel | Pacific Solutions FloorRight | Vimeo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعالانه</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | خدمات مشتریان و شخصی | زبان انگلیسی | تولید و فرآوری | امور اداری و مدیریت | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | زبان انگلیسی | تولید و فرآوری | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | زبردستی دستی | دقت کنترل | هماهنگی چند عضو | قدرت بالاتنه | زبردستی انگشتان | استقامت بدنی | بینایی نزدیک | قدرت ایستا | درک شفاهی | انعطاف‌پذیری بدنی | قدرت پویا | زمان عکس‌العمل | توجه انتخابی | بیان شفاهی</t>
+          <t>ثبات دست و بازو | مهارت دستی | دقت کنترل | هماهنگی چند عضو | قدرت تنه | مهارت انگشتان | استقامت | بینایی نزدیک | قدرت ایستا | درک شفاهی | انعطاف‌پذیری دامنه حرکت | قدرت پویا | زمان عکس‌العمل | توجه انتخابی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | صرف زمان برای خم شدن یا چرخاندن بدن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای به حالت زانو زده، چمباتمه، خمیده یا خزیده | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا منظم بودن | تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان، با دمای کنترل‌شده | صرف زمان برای راه رفتن یا دویدن | صرف زمان به حالت ایستاده | فراوانی تصمیم‌گیری | در معرض تجهیزات خطرناک | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | تماس با دیگران | مکالمات تلفنی | در معرض ارتعاش کل بدن | کار با یا مشارکت در یک گروه یا تیم کاری | سلامت و ایمنی سایر کارکنان | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | ارتباط با دیگران | مکالمات تلفنی | قرار گرفتن در معرض ارتعاش کل بدن | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بناهای آجرچین و بلوک‌چین | نجاران | فرش‌بندان | سیمان‌کاران و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | کارگران ساختمانی | نصب‌کنندگان دیوار خشک و تایل سقف | کف‌سازان، به جز فرش، چوب و تایل‌های سخت | پرداخت‌کاران مبلمان | کارگران پرداخت‌کار و سنباده‌زن دستی | کمک‌بناهای آجرچین، بلوک‌چین، سنگ‌چین و نصب‌کنندگان تایل و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | نقاشان ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | گچ‌کاران و بناهای سیمان‌کار | درزگیران دیوار خشک | کارگران موزاییک‌ساز و پرداخت‌کار | نصب‌کنندگان تایل و سنگ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های صنایع چوب، به جز اره‌کاری</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | نصّابان موکت و فرش | بنّایان سیمان‌کار و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | گچ‌کاران و بناهای سیمان‌کاری | تپرز | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tile and Stone Setters</t>
+          <t>کاشی‌کاران و سنگ‌کاران (Tile and Stone Setters)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Active Listening | تفکر انتقادی | ریاضیات | سخن‌گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | ریاضیات | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | ریاضیات | خدمات مشتریان و شخصی | طراحی</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | خدمات مشتری و شخصی | طراحی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تجسم فضایی | بینایی نزدیک | انعطاف‌پذیری بدنی | قدرت بالاتنه | حساسیت به مسئله | سازماندهی اطلاعات | بینایی دور | استقامت بدنی | قدرت ایستا | هماهنگی چند عضو | زبردستی انگشتان | زبردستی دستی | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | درک شفاهی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
+          <t>تجسم | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت تنه | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی دور | استقامت | قدرت ایستا | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | درک شفاهی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | اهمیت دقیق یا منظم بودن | صرف زمان برای به حالت زانو زده، چمباتمه، خمیده یا خزیده | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم شدن یا چرخاندن بدن | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در معرض آلاینده‌ها | صرف زمان به حالت ایستاده | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | کار با یا مشارکت در یک گروه یا تیم کاری | آزادی در تصمیم‌گیری | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بناهای آجرچین و بلوک‌چین | نجاران | فرش‌بندان | سیمان‌کاران و پرداخت‌کاران بتن | نصب‌کنندگان دیوار خشک و تایل سقف | کف‌سازان، به جز فرش, چوب و تایل‌های سخت | سنباده‌کشان و پرداخت‌کاران کف | پرداخت‌کاران مبلمان | شیشه‌بران | کمک‌بناهای آجرچین، بلوک‌چین، سنگ‌چین و نصب‌کنندگان تایل و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کاغذدیواری‌کنان | گچ‌کاران و بناهای سیمان‌کار | سقف‌سازان | سنگ‌فرش‌کنان قطعه‌ای | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سنگ‌چین‌ها | کارگران موزاییک‌ساز و پرداخت‌کار</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | نصّابان موکت و فرش | بنّایان سیمان‌کار و پرداخت‌کاران بتن | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | سنباده‌کاران و پرداخت‌کاران کف | پرداخت‌کاران مبلمان | شیشه‌بران | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کاغذدیواری‌کن‌ها | گچ‌کاران و بناهای سیمان‌کاری | سقف‌سازان | سنگ‌فرش‌کاران قطعه‌ای | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | بنّایان سنگ‌کار | کارگران و پرداخت‌کاران ترازو</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cement Masons and Concrete Finishers</t>
+          <t>بنّایان سیمان‌کار و پرداخت‌کاران بتن (Cement Masons and Concrete Finishers)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>پایش | سخن‌گفتن | تفکر انتقادی | گوش‌دادن فعالانه</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ساختمان و سازه | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | ساختمان و ساخت‌وساز | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>زبردستی دستی | قدرت بالاتنه | هماهنگی چند عضو | بینایی نزدیک | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری بدنی | قدرت پویا | استقامت بدنی | حساسیت به مسئله | استدلال قیاسی | سازماندهی اطلاعات | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک شفاهی | تشخیص گفتار | بینایی دور | قدرت ایستا | زبردستی انگشتان | توجه انتخابی | وضوح گفتار | درک عمق | هماهنگی عمومی بدن | زمان عکس‌العمل | کنترل سرعت | استدلال استقرایی</t>
+          <t>مهارت دستی | قدرت تنه | هماهنگی چند عضو | بینایی نزدیک | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری دامنه حرکت | قدرت پویا | استقامت | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | تجسم | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک شفاهی | تشخیص گفتار | بینایی دور | قدرت ایستا | مهارت انگشتان | توجه انتخابی | وضوح گفتار | درک عمق | هماهنگی کلی بدن | زمان عکس‌العمل | کنترل نرخ | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به حالت ایستاده | فضای باز، در معرض تمام شرایط آب و هوایی | در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا منظم بودن | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | سرعت کار تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | در معرض دمای بسیار گرم یا سرد | صرف زمان برای خم شدن یا چرخاندن بدن | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | تماس با دیگران | در معرض تجهیزات خطرناک | صرف زمان برای به حالت زانو زده، چمباتمه، خمیده یا خزیده | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | در خودروی روباز یا کار با تجهیزات روباز | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | موقعیت‌های درگیری</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای خم کردن یا چرخاندن بدن | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در یک وسیله نقلیه روباز یا کار با تجهیزات | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>بناهای آجرچین و بلوک‌چین | نجاران | کارگران ساختمانی | نصب‌کنندگان دیوار خشک و تایل سقف | کف‌سازان، به جز فرش، چوب و تایل‌های سخت | قالب‌ریزان و ماهیچه‌سازان ریخته‌گری | کمک‌بناهای آجرچین، بلوک‌چین، سنگ‌چین و نصب‌کنندگان تایل و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورهای تجهیزات روسازی، آسفالت و کوبش | گچ‌کاران و بناهای سیمان‌کار | تعمیرکاران مواد نسوز، به جز بناهای آجرچین | کارگران آرماتوربند و میلگرد | سقف‌سازان | سنگ‌فرش‌کنان قطعه‌ای | سنگ‌چین‌ها | کارگران اسکلت فلزی و فولادی | درزگیران دیوار خشک | کارگران موزاییک‌ساز و پرداخت‌کار | نصب‌کنندگان تایل و سنگ</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | گچ‌کاران و بناهای سیمان‌کاری | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | کارگران آهن تقویتی و میلگرد | سقف‌سازان | سنگ‌فرش‌کاران قطعه‌ای | بنّایان سنگ‌کار | کارگران سازه‌های آهنی و فولادی | تپرز | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0072_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0072_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | سخن گفتن | شنیدن فعال | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
+          <t>نظارت | درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساخت و ساز | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | طراحی | مکانیک | حمل‌ونقل | فروش و بازاریابی | ریاضیات</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مدیریت و اداره | طراحی | مکانیک | حمل و نقل | فروش و بازاریابی | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | مرتب‌سازی اطلاعات | استدلال استقرایی | بیان کتبی | تجسم فضایی | دید دور | وضوح گفتار | تشخیص گفتار | ثبات دست و بازو | دقت کنترل | چابکی دستی | تشخیص رنگ‌ها | توجه انتخابی | انعطاف‌پذیری ادراکی | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی | تجسم | بینایی دور | وضوح گفتار | تشخیص گفتار | ثبات دست و بازو | دقت کنترل | مهارت دستی | تشخیص رنگ بصری | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>معماران به‌جز منظر و دریایی | مهندسان عمران | مدیران ساخت و ساز | بازرسان ساختمان و ابنیه | مهندسان برق | برق‌کاران | ممیزان انرژی | مهندسان انرژی به‌جز باد و خورشید | سرپرستان رده‌اول مشاغل ساختمانی و استخراج | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | مدیران تولید انرژی زمین‌گرمایی | مهندسان صنایع | کارگران تعمیر و نگهداری عمومی | کارشناسان مدیریت پروژه | مهندسان سامانه‌های انرژی خورشیدی | نصابان سامانه‌های فتوولتائیک خورشیدی | کارشناسان فروش و ارزیابان خورشیدی | نصابان و تکنسین‌های سامانه‌های خورشیدی حرارتی | تکنسین‌های عایق‌بندی و بهینه‌سازی حرارتی | مدیران توسعه انرژی بادی</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | مهندسان عمران | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | مهندسان برق | برق‌کاران | ممیزان انرژی | مهندسان انرژی، به‌جز بادی و خورشیدی | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | مدیران تولید انرژی زمین‌گرمایی | مهندسان صنایع | کارگران عمومی تعمیرات و نگهداری تاسیسات | کارشناسان مدیریت پروژه | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | نصابان و تکنسین‌های عایق‌کاری و بهسازی مصرف انرژی | مدیران توسعه پروژه‌های انرژی بادی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | حساسیت به مسئله | استدلال قیاسی | ثبات دست و بازو | چابکی دستی | چابکی انگشتان | هماهنگی اندام‌ها | استدلال استقرایی | درک شفاهی | وضوح گفتار | توجه شنیداری | دید دور | وسعت دامنه حرکتی | قدرت عضلانی تنه | قدرت ایستا | زمان واکنش | توجه انتخابی | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری ادراکی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | روانی ایده‌ها | بیان کتبی | بیان شفاهی | درک کتبی</t>
+          <t>دقت کنترل | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | هماهنگی چند عضو | استدلال استقرایی | درک شفاهی | وضوح گفتار | توجه شنیداری | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | بیان کتبی | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سامانه‌های هوایی | نصابان و تعمیرکاران سیستم‌های کنترل و شیرآلات به‌جز درهای مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و نصابان سیستم‌های سرمایشی، گرمایشی و تهویه مطبوع | کمک‌برق‌کاران | کمک‌نصابان، تعمیرکاران و نگه‌دارندگان | کمک‌لوله‌کشان، خطوط لوله و لوله‌کشان صنعتی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران تعمیر و نگهداری عمومی | نصابان و ترازکاران ماشین‌آلات سنگین (میلرایت‌ها) | لوله‌کشان، لوله‌کشان صنعتی و اتصالات بخار | ورق‌کاران و نصابان قطعات فلزی | مهندسان تأسیسات ثابت و اپراتورهای دیگ بخار | کارگران سازه‌های اسکلت فلزی و فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات جوشکاری و لحیم‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کمک‌برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | کارگران ورق‌کاری فلزی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ساخت و ساز | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | تولید و فرآوری | طراحی | مدیریت و امور اداری | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | تولید و فرآوری | طراحی | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>قدرت عضلانی تنه | وسعت دامنه حرکتی | دید نزدیک | ثبات دست و بازو | چابکی دستی | قدرت ایستا | تجسم فضایی | هماهنگی اندام‌ها | قدرت دینامیک | مرتب‌سازی اطلاعات | چابکی انگشتان | حساسیت به مسئله | تعادل کلی بدن | دید دور | هماهنگی کلی بدن | استقامت بدنی | دقت کنترل | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی | درک کتبی</t>
+          <t>قدرت تنه | انعطاف‌پذیری دامنه حرکت | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | قدرت ایستا | تجسم | هماهنگی چند عضو | قدرت پویا | ترتیب‌دهی اطلاعات | مهارت انگشتان | حساسیت به مسئله | تعادل کلی بدن | بینایی دور | هماهنگی کلی بدن | استقامت | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>دیگ‌سازان و مخزن‌سازان صنعتی | نجاران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساده ساختمانی | نصابان صفحات گچی (کناف) و تایل‌های سقفی | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | شیشه‌بران و شیشه‌گذاران | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تأسیسات مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران به‌جز فلز و پلاستیک | سفیدکاران و گچ‌کاران سنتی و پلیمری | تعمیرکاران مواد نسوز به‌جز بنایان آجر | کارگران آرماتوربندی و تقویت اسکلت | ورق‌کاران و نصابان قطعات فلزی | سنگ‌کاران ساختمانی | کارگران سازه‌های اسکلت فلزی و فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | موزاییک‌سازان، واش‌بتن‌کاران و نصابان بتن درجا | کاشی‌کاران و سنگ‌کاران ظریف</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | شیشه‌بران و نصابان شیشه | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | سفیدکاران و گچ‌کاران نما | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | آرماتوربندان و نصابان میلگرد | کارگران ورق‌کاری فلزی | سنگ‌کاران ساختمانی | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | نظارت | ریاضیات | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نظارت | ریاضیات | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ساخت و ساز | طراحی | ریاضیات | مکانیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی</t>
+          <t>ساختمان و ساخت‌وساز | طراحی | ریاضیات | مکانیک | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>قدرت ایستا | قدرت عضلانی تنه | دید نزدیک | ثبات دست و بازو | چابکی دستی | حساسیت به مسئله | تجسم فضایی | استقامت بدنی | دید دور | وسعت دامنه حرکتی | هماهنگی اندام‌ها | مرتب‌سازی اطلاعات | درک شفاهی | توجه انتخابی | چابکی انگشتان | قدرت دینامیک | انعطاف‌پذیری طبقه‌بندی | استدلال قیاسی | تعادل کلی بدن | دقت کنترل | بیان شفاهی | وضوح گفتار | تشخیص گفتار</t>
+          <t>قدرت ایستا | قدرت تنه | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | حساسیت به مسئله | تجسم | استقامت | بینایی دور | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | ترتیب‌دهی اطلاعات | درک شفاهی | توجه انتخابی | مهارت انگشتان | قدرت پویا | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | تعادل کلی بدن | دقت کنترل | بیان شفاهی | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بنایان و سفت‌کاران ساختمان | نجاران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساده ساختمانی | نصابان صفحات گچی (کناف) و تایل‌های سقفی | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | شیشه‌بران و شیشه‌گذاران | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | کمک‌نجاران | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران به‌جز فلز و پلاستیک | سفیدکاران و گچ‌کاران سنتی و پلیمری | تعمیرکاران مواد نسوز به‌جز بنایان آجر | کارگران آرماتوربندی و تقویت اسکلت | ایزوگام‌کاران و عایق‌کاران رطوبتی سقف | سنگ‌فرش‌کاران و بلوک‌فرش‌کاران راه‌ها | سنگ‌تراشان و حجّاران صنعتی | کارگران سازه‌های اسکلت فلزی و فولادی | موزاییک‌سازان، واش‌بتن‌کاران و نصابان بتن درجا | کاشی‌کاران و سنگ‌کاران ظریف</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | شیشه‌بران و نصابان شیشه | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | سفیدکاران و گچ‌کاران نما | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | آرماتوربندان و نصابان میلگرد | عایق‌کاران و نصابان پوشش‌های سقفی | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | سنگ‌تراشان و حکاکان صنعتی سنگ | اسکلت‌سازان و نصابان سازه‌های فولادی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | یادگیری فعال | ریاضیات</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ساخت و ساز | ریاضیات | مدیریت و امور اداری | طراحی | مهندسی و فناوری | ایمنی و امنیت عمومی | مکانیک | آموزش و تدریس | خدمات مشتریان و خدمات فردی | فیزیک</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | مدیریت و اداره | طراحی | مهندسی و فناوری | ایمنی و امنیت عمومی | مکانیک | آموزش و پرورش | خدمات مشتری و شخصی | فیزیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | تجسم فضایی | دید نزدیک | چابکی دستی | چابکی انگشتان | قدرت عضلانی تنه | ثبات دست و بازو | مرتب‌سازی اطلاعات | استدلال قیاسی | دید دور | هماهنگی اندام‌ها | بیان شفاهی | درک شفاهی | قدرت ایستا | استدلال استقرایی | زمان واکنش | دقت کنترل | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | وضوح گفتار | تشخیص گفتار | قدرت انفجاری | سرعت ادراک | انعطاف‌پذیری ادراکی | درک کتبی</t>
+          <t>حساسیت به مسئله | تجسم | بینایی نزدیک | مهارت دستی | مهارت انگشتان | قدرت تنه | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | بینایی دور | هماهنگی چند عضو | بیان شفاهی | درک شفاهی | قدرت ایستا | استدلال استقرایی | زمان عکس‌العمل | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | قدرت انفجاری | سرعت ادراکی | انعطاف‌پذیری بستار | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سامانه‌های هوایی | بنایان و سفت‌کاران ساختمان | کابینت‌سازان و نجاران کارگاهی | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساده ساختمانی | نصابان صفحات گچی (کناف) و تایل‌های سقفی | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | شیشه‌بران و شیشه‌گذاران | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | کمک‌نجاران | کمک‌لوله‌کشان، خطوط لوله و لوله‌کشان صنعتی | عایق‌کاران کف، سقف و دیوار | خط‌کشان و شابلون‌کاران فلز و پلاستیک | سفیدکاران و گچ‌کاران سنتی و پلیمری | کارگران آرماتوربندی و تقویت اسکلت | ایزوگام‌کاران و عایق‌کاران رطوبتی سقف | ورق‌کاران و نصابان قطعات فلزی | کارگران سازه‌های اسکلت فلزی و فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | کاشی‌کاران و سنگ‌کاران ظریف</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | بنایان و سفت‌کاران ساختمان | کابینت‌سازان و نجاران کارگاهی | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | شیشه‌بران و نصابان شیشه | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران کف، سقف و دیوار | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | سفیدکاران و گچ‌کاران نما | آرماتوربندان و نصابان میلگرد | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات | مدیریت و امور اداری | زبان انگلیسی | ساخت و ساز | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره | زبان انگلیسی | ساختمان و ساخت‌وساز | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>وسعت دامنه حرکتی | قدرت عضلانی تنه | حساسیت به مسئله | دید نزدیک | قدرت ایستا | تشخیص گفتار | تجسم فضایی | ثبات دست و بازو | چابکی دستی | بیان شفاهی | استقامت بدنی | هماهنگی اندام‌ها | چابکی انگشتان | ادراک عمق | دید دور | قدرت دینامیک | توجه انتخابی | مرتب‌سازی اطلاعات | استدلال قیاسی | درک شفاهی</t>
+          <t>انعطاف‌پذیری دامنه حرکت | قدرت تنه | حساسیت به مسئله | بینایی نزدیک | قدرت ایستا | تشخیص گفتار | تجسم | ثبات دست و بازو | مهارت دستی | بیان شفاهی | استقامت | هماهنگی چند عضو | مهارت انگشتان | درک عمق | بینایی دور | قدرت پویا | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بنایان و سفت‌کاران ساختمان | نجاران | بتن‌ریزان و پرداخت‌کاران بتن | نصابان صفحات گچی (کناف) و تایل‌های سقفی | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | رنگ‌کاران و پرداخت‌کاران چوب و مبلمان | شیشه‌بران و شیشه‌گذاران | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تأسیسات مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران به‌جز فلز و پلاستیک | نصابان کاغذ دیواری | سفیدکاران و گچ‌کاران سنتی و پلیمری | ایزوگام‌کاران و عایق‌کاران رطوبتی سقف | سنگ‌فرش‌کاران و بلوک‌فرش‌کاران راه‌ها | سنگ‌تراشان و حجّاران صنعتی | موزاییک‌سازان، واش‌بتن‌کاران و نصابان بتن درجا | کاشی‌کاران و سنگ‌کاران ظریف | رویه‌کوبان مبل و روکش‌کاران</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | شیشه‌بران و نصابان شیشه | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | نصابان کاغذ دیواری | سفیدکاران و گچ‌کاران نما | عایق‌کاران و نصابان پوشش‌های سقفی | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | سنگ‌تراشان و حکاکان صنعتی سنگ | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن</t>
+          <t>گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ساخت و ساز | خدمات مشتریان و خدمات فردی | ریاضیات | مکانیک | تولید و فرآوری | طراحی</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | ریاضیات | مکانیک | تولید و فرآوری | طراحی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | وسعت دامنه حرکتی | ثبات دست و بازو | درک شفاهی | قدرت ایستا | چابکی انگشتان | چابکی دستی | حساسیت به مسئله | بیان شفاهی | وضوح گفتار | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | درک شفاهی | قدرت ایستا | مهارت انگشتان | مهارت دستی | حساسیت به مسئله | بیان شفاهی | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بنایان و سفت‌کاران ساختمان | نجاران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | نصابان صفحات گچی (کناف) و تایل‌های سقفی | ساب‌زنان و پرداخت‌کاران کف | رنگ‌کاران و پرداخت‌کاران چوب و مبلمان | شیشه‌بران و شیشه‌گذاران | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تأسیسات مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران به‌جز فلز و پلاستیک | نصابان کاغذ دیواری | سفیدکاران و گچ‌کاران سنتی و پلیمری | ایزوگام‌کاران و عایق‌کاران رطوبتی سقف | سنگ‌فرش‌کاران و بلوک‌فرش‌کاران راه‌ها | ورق‌کاران و نصابان قطعات فلزی | سنگ‌تراشان و حجّاران صنعتی | موزاییک‌سازان، واش‌بتن‌کاران و نصابان بتن درجا | کاشی‌کاران و سنگ‌کاران ظریف</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | نصابان دیوار کاذب و تایل سقف | ساب‌زنان و پرداخت‌کاران کف | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | شیشه‌بران و نصابان شیشه | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | نصابان کاغذ دیواری | سفیدکاران و گچ‌کاران نما | عایق‌کاران و نصابان پوشش‌های سقفی | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | کارگران ورق‌کاری فلزی | سنگ‌تراشان و حکاکان صنعتی سنگ | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FloorCOST Estimator for Excel | Flooring Technologies QFloors | Measure Square | Pacific Solutions FloorRight | Microsoft Excel | نرم‌افزار نقشه‌کشی و پلان کف | Vimeo</t>
+          <t>نرم‌افزار برنامه‌ریزی چیدمان طبقات | Flooring Technologies QFloors | Measure Square | Pacific Solutions FloorRight | Microsoft Excel | نرم‌افزار نقشه‌کشی و پلان کف | Vimeo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ساخت و ساز | خدمات مشتریان و خدمات فردی | زبان انگلیسی | تولید و فرآوری | مدیریت و امور اداری | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | زبان انگلیسی | تولید و فرآوری | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | دقت کنترل | هماهنگی اندام‌ها | قدرت عضلانی تنه | چابکی انگشتان | استقامت بدنی | دید نزدیک | قدرت ایستا | درک شفاهی | وسعت دامنه حرکتی | قدرت دینامیک | زمان واکنش | توجه انتخابی | بیان شفاهی</t>
+          <t>ثبات دست و بازو | مهارت دستی | دقت کنترل | هماهنگی چند عضو | قدرت تنه | مهارت انگشتان | استقامت | بینایی نزدیک | قدرت ایستا | درک شفاهی | انعطاف‌پذیری دامنه حرکت | قدرت پویا | زمان عکس‌العمل | توجه انتخابی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بنایان و سفت‌کاران ساختمان | نجاران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و مراقبان دستگاه‌های پوشش‌دهی، رنگ‌کاری و پاشش | کارگران ساده ساختمانی | نصابان صفحات گچی (کناف) و تایل‌های سقفی | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | رنگ‌کاران و پرداخت‌کاران چوب و مبلمان | کارگران سنگ‌زنی، پولیش و پرداخت دستی | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | عایق‌کاران کف، سقف و دیوار | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران به‌جز فلز و پلاستیک | نقاشان ساختمان و کارهای تعمیراتی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین | سفیدکاران و گچ‌کاران سنتی و پلیمری | درزگیران و بتونه‌کاران کناف و دیوار | موزاییک‌سازان، واش‌بتن‌کاران و نصابان بتن درجا | کاشی‌کاران و سنگ‌کاران ظریف | تنظیم‌کنندگان و اپراتورهای ماشین‌آلات چوب‌بری به‌جز اره‌کشی</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | سفیدکاران و گچ‌کاران نما | بتونه‌کاران و درزگیران دیوار کاذب | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | ریاضیات | سخن گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | ریاضیات | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساخت و ساز | ریاضیات | خدمات مشتریان و خدمات فردی | طراحی</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | خدمات مشتری و شخصی | طراحی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | وسعت دامنه حرکتی | قدرت عضلانی تنه | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید دور | استقامت بدنی | قدرت ایستا | هماهنگی اندام‌ها | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | انعطاف‌پذیری طبقه‌بندی | درک شفاهی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ‌ها | دقت کنترل | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
+          <t>تجسم | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت تنه | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی دور | استقامت | قدرت ایستا | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | درک شفاهی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | دقت کنترل | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بنایان و سفت‌کاران ساختمان | نجاران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | نصابان صفحات گچی (کناف) و تایل‌های سقفی | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | رنگ‌کاران و پرداخت‌کاران چوب و مبلمان | شیشه‌بران و شیشه‌گذاران | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تأسیسات مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران به‌جز فلز و پلاستیک | نصابان کاغذ دیواری | سفیدکاران و گچ‌کاران سنتی و پلیمری | ایزوگام‌کاران و عایق‌کاران رطوبتی سقف | سنگ‌فرش‌کاران و بلوک‌فرش‌کاران راه‌ها | سنگ‌تراشان و حجّاران صنعتی | سنگ‌کاران ساختمانی | موزاییک‌سازان، واش‌بتن‌کاران و نصابان بتن درجا</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | شیشه‌بران و نصابان شیشه | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | نصابان کاغذ دیواری | سفیدکاران و گچ‌کاران نما | عایق‌کاران و نصابان پوشش‌های سقفی | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | سنگ‌تراشان و حکاکان صنعتی سنگ | سنگ‌کاران ساختمانی | موزاییک‌کاران و پرداخت‌کاران terrazzo</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | تفکر انتقادی | شنیدن فعال</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ساخت و ساز | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | ساختمان و ساخت‌وساز | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>چابکی دستی | قدرت عضلانی تنه | هماهنگی اندام‌ها | دید نزدیک | ثبات دست و بازو | دقت کنترل | وسعت دامنه حرکتی | قدرت دینامیک | استقامت بدنی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | بیان شفاهی | درک شفاهی | تشخیص گفتار | دید دور | قدرت ایستا | چابکی انگشتان | توجه انتخابی | وضوح گفتار | ادراک عمق | هماهنگی کلی بدن | زمان واکنش | کنترل نرخ تغییرات | استدلال استقرایی</t>
+          <t>مهارت دستی | قدرت تنه | هماهنگی چند عضو | بینایی نزدیک | ثبات دست و بازو | دقت کنترل | انعطاف‌پذیری دامنه حرکت | قدرت پویا | استقامت | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | تجسم | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک شفاهی | تشخیص گفتار | بینایی دور | قدرت ایستا | مهارت انگشتان | توجه انتخابی | وضوح گفتار | درک عمق | هماهنگی کلی بدن | زمان عکس‌العمل | کنترل نرخ | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>بنایان و سفت‌کاران ساختمان | نجاران | کارگران ساده ساختمانی | نصابان صفحات گچی (کناف) و تایل‌های سقفی | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | عایق‌کاران کف، سقف و دیوار | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران به‌جز فلز و پلاستیک | اپراتورهای ماشین‌آلات روسازی، آسفالت و تراکم بتن | سفیدکاران و گچ‌کاران سنتی و پلیمری | تعمیرکاران مواد نسوز به‌جز بنایان آجر | کارگران آرماتوربندی و تقویت اسکلت | ایزوگام‌کاران و عایق‌کاران رطوبتی سقف | سنگ‌فرش‌کاران و بلوک‌فرش‌کاران راه‌ها | سنگ‌کاران ساختمانی | کارگران سازه‌های اسکلت فلزی و فولادی | درزگیران و بتونه‌کاران کناف و دیوار | موزاییک‌سازان، واش‌بتن‌کاران و نصابان بتن درجا | کاشی‌کاران و سنگ‌کاران ظریف</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | سفیدکاران و گچ‌کاران نما | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | آرماتوربندان و نصابان میلگرد | عایق‌کاران و نصابان پوشش‌های سقفی | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | سنگ‌کاران ساختمانی | اسکلت‌سازان و نصابان سازه‌های فولادی | بتونه‌کاران و درزگیران دیوار کاذب | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
